--- a/public/templates/measure_target_template.xlsx
+++ b/public/templates/measure_target_template.xlsx
@@ -397,122 +397,129 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="40.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="20.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:S2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>No</v>
+      </c>
+      <c r="B1" t="str">
         <v>년도</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>주기</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
+        <v>지정지청</v>
+      </c>
+      <c r="E1" t="str">
         <v>코드</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
+        <v>사업자등록번호</v>
+      </c>
+      <c r="G1" t="str">
+        <v>산재관리번호</v>
+      </c>
+      <c r="H1" t="str">
         <v>사업장명</v>
       </c>
-      <c r="E1" t="str">
+      <c r="I1" t="str">
         <v>소재지</v>
       </c>
-      <c r="F1" t="str">
-        <v>업종</v>
-      </c>
-      <c r="G1" t="str">
-        <v>담당자</v>
-      </c>
-      <c r="H1" t="str">
-        <v>연락처</v>
-      </c>
-      <c r="I1" t="str">
-        <v>회사전화</v>
-      </c>
       <c r="J1" t="str">
-        <v>계획담당자</v>
+        <v>실시여부</v>
       </c>
       <c r="K1" t="str">
-        <v>관할청</v>
+        <v>국고결과</v>
       </c>
       <c r="L1" t="str">
-        <v>실시여부</v>
+        <v>계획담당</v>
       </c>
       <c r="M1" t="str">
-        <v>측정예정월</v>
+        <v>업종분류</v>
       </c>
       <c r="N1" t="str">
-        <v>측정확정일</v>
+        <v>담당자명</v>
       </c>
       <c r="O1" t="str">
+        <v>휴대폰</v>
+      </c>
+      <c r="P1" t="str">
+        <v>전화번호</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>보고서 담당</v>
+      </c>
+      <c r="R1" t="str">
+        <v>향후측정주기</v>
+      </c>
+      <c r="S1" t="str">
         <v>비고</v>
       </c>
     </row>
     <row r="2">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>2026</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>상반기</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
+        <v>천안지청</v>
+      </c>
+      <c r="E2" t="str">
         <v>H0001</v>
       </c>
-      <c r="D2" t="str">
+      <c r="F2" t="str">
+        <v>106-86-01863</v>
+      </c>
+      <c r="G2" t="str">
+        <v>922-06-96284-7</v>
+      </c>
+      <c r="H2" t="str">
         <v>(주)예시사업장</v>
       </c>
-      <c r="E2" t="str">
+      <c r="I2" t="str">
         <v>서울시 구로구 디지털로</v>
       </c>
-      <c r="F2" t="str">
+      <c r="J2" t="str">
+        <v>미실시</v>
+      </c>
+      <c r="K2" t="str">
+        <v>비대상</v>
+      </c>
+      <c r="L2" t="str">
+        <v>이주형</v>
+      </c>
+      <c r="M2" t="str">
         <v>소프트웨어개발</v>
       </c>
-      <c r="G2" t="str">
+      <c r="N2" t="str">
         <v>김담당</v>
       </c>
-      <c r="H2" t="str">
+      <c r="O2" t="str">
         <v>010-1234-5678</v>
       </c>
-      <c r="I2" t="str">
+      <c r="P2" t="str">
         <v>02-123-4567</v>
       </c>
-      <c r="J2" t="str">
+      <c r="Q2" t="str">
         <v>이주형</v>
       </c>
-      <c r="K2" t="str">
-        <v>서울관악</v>
-      </c>
-      <c r="L2" t="str">
-        <v>미실시</v>
-      </c>
-      <c r="M2" t="str">
-        <v>3월</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
+      <c r="R2" t="str">
+        <v>6개월</v>
+      </c>
+      <c r="S2" t="str">
         <v>특이사항 없음</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S2"/>
   </ignoredErrors>
 </worksheet>
 </file>